--- a/docs/04-项目管理与规范/planning/K8S-AI 开发计划.xlsx
+++ b/docs/04-项目管理与规范/planning/K8S-AI 开发计划.xlsx
@@ -14,8 +14,12 @@
   <sheets>
     <sheet name="1~3期" sheetId="1" r:id="rId1"/>
     <sheet name="四期" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="四期 (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">四期!$A$2:$J$83</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="708">
   <si>
     <t>K8S-AI 运维Agent开发计划</t>
   </si>
@@ -391,16 +395,934 @@
     <t>M5；目标 v3.0.0</t>
   </si>
   <si>
+    <t>K8S-AI 运维Agent开发计划（四期·平台化）</t>
+  </si>
+  <si>
+    <t>四期需求范围复审与关键决策签收</t>
+  </si>
+  <si>
+    <t>P0 规格与设计基线</t>
+  </si>
+  <si>
+    <t>复审四期需求与范围，签收 D-01~D-18 关键决策，并回写需求文档</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：需求 v1.3；预估：0.5d；验收：所有推荐值决策有结论并已回写文档；说明：含审批/授权新增决策 D-15~D-18</t>
+  </si>
+  <si>
+    <t>统一 API 契约冻结（/api/v1）</t>
+  </si>
+  <si>
+    <t>前端可基于该契约 mock 开发，错误码与权限码定义完整</t>
+  </si>
+  <si>
+    <t>冻结认证、集群、Skill、配置、用户、审批、审计、Chat SSE 与通用错误/分页契约</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P0.1；预估：1d；验收：正式 API 边界统一为 /api/v1</t>
+  </si>
+  <si>
+    <t>数据存储接口与迁移策略冻结</t>
+  </si>
+  <si>
+    <t>业务层只依赖接口；迁移可升级且不无提示丢数据</t>
+  </si>
+  <si>
+    <t>冻结 Store 接口、SQLite/MySQL 表结构与版本迁移策略</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P0.1；预估：1d</t>
+  </si>
+  <si>
+    <t>实时事件契约与三期事件映射冻结</t>
+  </si>
+  <si>
+    <t>冻结 session/turn/step 事件目录，以及三期 answer-delta、reasoning-delta、tool-call、tool-result 的映射</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P0.2；预估：0.5d；验收：每个事件都带 session/turn/step/timestamp/type；旧事件可映射</t>
+  </si>
+  <si>
+    <t>前端信息架构与目录规范</t>
+  </si>
+  <si>
+    <t>确定 web/ 目录、侧栏信息架构与前端三视图权限（路由/组件/按钮）</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P0.2；预估：0.5d；验收：一级路由与需求 §10/§11 对应；侧栏按工作区/治理/平台管理分组；说明：权限仅做 UX，后端强校验</t>
+  </si>
+  <si>
+    <t>三期数据与配置迁移基线</t>
+  </si>
+  <si>
+    <t>梳理旧 config.yaml、Skill、Session/Chat、Approval、Report 与配置目录的迁移方案</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P0.1；预估：0.5d；验收：每个数据源都有「可迁移」或「显式拒绝」两条结论，验收用例可追踪</t>
+  </si>
+  <si>
+    <t>前端工程骨架（Vite+Vue3+TS）与原型评审</t>
+  </si>
+  <si>
+    <t>P1 平台底座</t>
+  </si>
+  <si>
+    <t>npm run build 与 lint 通过；基础路由可访问</t>
+  </si>
+  <si>
+    <t>搭建 web/ 工程、lint/format/构建链；完成平台化原型与前端方案评审</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P0.5；预估：1d</t>
+  </si>
+  <si>
+    <t>统一 Store 与 SQLite 驱动</t>
+  </si>
+  <si>
+    <t>用户/会话/审计/配置等核心实体可读写，迁移可重复执行</t>
+  </si>
+  <si>
+    <t>实现 internal/store 统一接口、SQLite 驱动与幂等表结构迁移</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P0.3；预估：1d</t>
+  </si>
+  <si>
+    <t>MySQL 驱动与双库统一迁移</t>
+  </si>
+  <si>
+    <t>两种驱动行为等价；MySQL 集成用例可通过环境变量启用</t>
+  </si>
+  <si>
+    <t>抽出共享方言层，实现 MySQL 与 SQLite 同一套表结构与迁移</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P1.2；预估：1d；验收：生产正式部署优先 MySQL</t>
+  </si>
+  <si>
+    <t>HTTP 基础中间件</t>
+  </si>
+  <si>
+    <t>实现请求 ID、统一响应信封、分页解析、CORS 与认证上下文占位</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P1.2；预估：0.5d；验收：接口响应结构与错误信封统一</t>
+  </si>
+  <si>
+    <t>用户账号与登录认证</t>
+  </si>
+  <si>
+    <t>可登录获取会话凭证，密码不落明文</t>
+  </si>
+  <si>
+    <t>用户/角色模型、argon2id 密码哈希、登录态与 /auth/login|logout|me</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P1.2；预估：1d</t>
+  </si>
+  <si>
+    <t>后端权限门禁（角色-权限-策略）</t>
+  </si>
+  <si>
+    <t>未登录 401、越权 403、未登记路由默认拒绝</t>
+  </si>
+  <si>
+    <t>实现 Role→Permission→Policy 判定与服务端统一门禁</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P1.5；预估：0.5d</t>
+  </si>
+  <si>
+    <t>会话/回合/步骤模型与存储</t>
+  </si>
+  <si>
+    <t>刷新或重开会话可完整回放过程</t>
+  </si>
+  <si>
+    <t>建立 Session/Turn/Step 三模型状态机与入库、回放能力</t>
+  </si>
+  <si>
+    <t>Agent 运行时生命周期落库</t>
+  </si>
+  <si>
+    <t>每轮 Agent 执行过程可追溯，落库失败不阻塞主流程</t>
+  </si>
+  <si>
+    <t>把推理、工具、观察、审批、回答等生命周期埋点接入持久化</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P1.7；预估：1d</t>
+  </si>
+  <si>
+    <t>统一事件路由与三期旧事件映射</t>
+  </si>
+  <si>
+    <t>新事件可下发，旧前端仍可消费；负载统一脱敏</t>
+  </si>
+  <si>
+    <t>实现四期统一事件封装、序列化与三期旧事件双向映射，出站统一脱敏</t>
+  </si>
+  <si>
+    <t>配置中心服务底座</t>
+  </si>
+  <si>
+    <t>分组可读可改；非法值整批拒绝；变更写审计且不含取值</t>
+  </si>
+  <si>
+    <t>实现 7 组配置目录（模型/Skill/审批/Memory/保留/MCP/运维）与整批校验落库</t>
+  </si>
+  <si>
+    <t>审计事件模型与系统事件写入</t>
+  </si>
+  <si>
+    <t>关键动作均可审计，写前脱敏</t>
+  </si>
+  <si>
+    <t>补齐审计事件字段与分类映射，接入登录、登出、配置变更、工具调用、Skill 运行等事件</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P1.2；预估：1d；验收：集群变更审计随 P3.2 一并落地</t>
+  </si>
+  <si>
+    <t>数据库迁移命令与三期数据导入</t>
+  </si>
+  <si>
+    <t>可重复执行；不可迁移数据显式报告</t>
+  </si>
+  <si>
+    <t>提供显式一次性迁移入口，导入三期会话、审计、配置等数据</t>
+  </si>
+  <si>
+    <t>平台底座测试集（存储/认证/Agent/事件）</t>
+  </si>
+  <si>
+    <t>补齐 Store、认证、Agent 生命周期与事件契约测试</t>
+  </si>
+  <si>
+    <t>里程碑：M1；依赖：P1.12；预估：1d；验收：go test ./... 全绿，关键契约有回归用例</t>
+  </si>
+  <si>
+    <t>应用整体布局与侧边栏</t>
+  </si>
+  <si>
+    <t>P2 Web Shell</t>
+  </si>
+  <si>
+    <t>布局与信息架构一致，用户信息位于右上角</t>
+  </si>
+  <si>
+    <t>实现平台主框架、三组侧栏与用户菜单</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P1.1；预估：1d</t>
+  </si>
+  <si>
+    <t>登录页与前端路由守卫</t>
+  </si>
+  <si>
+    <t>未登录自动跳转登录页；登录后可进入主界面</t>
+  </si>
+  <si>
+    <t>实现登录页、令牌持久化与未登录跳转</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.1, P1.5；预估：0.5d</t>
+  </si>
+  <si>
+    <t>前端 API 客户端与分页类型</t>
+  </si>
+  <si>
+    <t>封装统一请求、认证头、响应信封解析、错误归一与分页</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P1.4；预估：0.5d；验收：401 自动清理登录态并跳转；错误码可直接展示</t>
+  </si>
+  <si>
+    <t>会话列表与历史会话加载</t>
+  </si>
+  <si>
+    <t>可切换历史会话，列表与后端数据一致</t>
+  </si>
+  <si>
+    <t>实现会话新建、选择、删除、重命名与历史消息加载</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.3；预估：1d</t>
+  </si>
+  <si>
+    <t>实时消息流客户端与事件归一</t>
+  </si>
+  <si>
+    <t>断线重连不丢重复消息；旧事件可映射为统一事件</t>
+  </si>
+  <si>
+    <t>实现 SSE 连接、断线重连、历史快照重建与旧事件归一</t>
+  </si>
+  <si>
+    <t>对话消息流与报告渲染</t>
+  </si>
+  <si>
+    <t>实现消息时间线、增量分片聚合成单块报告、流式与终态一致</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.5；预估：0.5d；验收：最终报告与流式过程一致，不出现重复报告或卡在生成中</t>
+  </si>
+  <si>
+    <t>Agent 执行步骤卡与思考面板</t>
+  </si>
+  <si>
+    <t>有多少步骤展示多少；思考框推理中展开、报告后折叠</t>
+  </si>
+  <si>
+    <t>实现推理、工具、观察、审批、回答等步骤卡片与思考面板展开收起</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.5；预估：1d</t>
+  </si>
+  <si>
+    <t>工具调用结果卡与敏感值遮蔽</t>
+  </si>
+  <si>
+    <t>实现工具名、命令摘要、风险、耗时与结构化结果展示</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.7；预估：0.5d；验收：结果即时展开并保持；Secret 值不回显</t>
+  </si>
+  <si>
+    <t>审批卡片与交互</t>
+  </si>
+  <si>
+    <t>可完成批准与拒绝；无权用户按钮隐藏且后端仍强校验</t>
+  </si>
+  <si>
+    <t>实现审批卡：风险、工具、参数摘要、目标资源、批准/拒绝与 Secret 占位输入</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P1.6, P2.7；预估：1d</t>
+  </si>
+  <si>
+    <t>消息输入区与运行控制</t>
+  </si>
+  <si>
+    <t>实现多行输入、发送、运行中停止与会话绑定</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.6；预估：0.5d；验收：发送后进入新一轮执行，状态由事件流驱动</t>
+  </si>
+  <si>
+    <t>三期聊天行为回归验证</t>
+  </si>
+  <si>
+    <t>对比三期工具卡、思考框、审批卡与报告行为，固化差异</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.8, P2.9；预估：0.5d；验收：迁移期聊天行为可完整运行且与三期一致</t>
+  </si>
+  <si>
+    <t>前端测试与构建门禁</t>
+  </si>
+  <si>
+    <t>关键交互有测试；lint 与 build 全绿</t>
+  </si>
+  <si>
+    <t>补齐组件与交互用例，纳入 lint/typecheck/build 门禁</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P2.11；预估：1d</t>
+  </si>
+  <si>
+    <t>会话 Token 用量统计与展示</t>
+  </si>
+  <si>
+    <t>持久化每会话 Token 用量并在界面展示</t>
+  </si>
+  <si>
+    <t>里程碑：M2；依赖：P1.7, P1.8；预估：0.5d；验收：刷新或重开会话后用量仍可读；不含敏感数据</t>
+  </si>
+  <si>
+    <t>集群接入模型与凭据加密存储</t>
+  </si>
+  <si>
+    <t>P3 平台能力</t>
+  </si>
+  <si>
+    <t>kubeconfig 加密存储，不进入 LLM/会话/审计</t>
+  </si>
+  <si>
+    <t>实现 Cluster/Credential 模型，kubeconfig 加密落库且与集群分离</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P1.2；预估：1d</t>
+  </si>
+  <si>
+    <t>集群配置导入、校验与连接测试</t>
+  </si>
+  <si>
+    <t>可解析、可校验、可连接；错误原因清晰</t>
+  </si>
+  <si>
+    <t>支持上传或粘贴 kubeconfig，解析校验并执行连接测试</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.1；预估：1d</t>
+  </si>
+  <si>
+    <t>集群状态查询接口</t>
+  </si>
+  <si>
+    <t>提供集群列表、当前集群、版本与健康状态查询</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.2；预估：0.5d；验收：单集群状态可读；数据模型预留多集群</t>
+  </si>
+  <si>
+    <t>集群管理页面</t>
+  </si>
+  <si>
+    <t>页面不出现 kubeconfig 明文；失败与断连可提示</t>
+  </si>
+  <si>
+    <t>实现集群上传/粘贴、连接测试、状态展示与删除</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.2, P2.3；预估：1d</t>
+  </si>
+  <si>
+    <t>Skill 平台数据模型与存储</t>
+  </si>
+  <si>
+    <t>Skill 无执行动作字段；架构测试继续锁定边界</t>
+  </si>
+  <si>
+    <t>建立内置/自定义 Skill 类型、来源、版本、启停、校验状态与运行统计</t>
+  </si>
+  <si>
+    <t>Skill 导入与校验（YAML / SKILL.md / 技能包）</t>
+  </si>
+  <si>
+    <t>非法内容明确报错；技能包脚本一律不执行；路径穿越等风险整包拒绝</t>
+  </si>
+  <si>
+    <t>支持结构化 YAML 导入、标准 SKILL.md 文本导入与技能包 zip 导入，并做严格校验</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.5；预估：1.5d；验收：已合并 P3.6 与 P3.8.1/P3.8.2 细项</t>
+  </si>
+  <si>
+    <t>Skill 启停、命中记录与前端管理页</t>
+  </si>
+  <si>
+    <t>实现启停开关、命中统计展示与 Skill 管理页面（含上传与资产展示）</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.6；预估：1d；验收：启停即时生效；命中与风险记录可查；页面可完成导入与查看；说明：已合并 P3.7 与 P3.8.4 细项</t>
+  </si>
+  <si>
+    <t>Skill 在对话中被自动/显式调用</t>
+  </si>
+  <si>
+    <t>相关场景能自动命中 Skill；@ 指定可用；命中写 SKILL_RUN 审计</t>
+  </si>
+  <si>
+    <t>实现对话前意图匹配、@技能名显式指定、只读技能查询工具与命中审计</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.6；预估：1.5d；验收：已合并 P3.8 与 P3.8.3 细项</t>
+  </si>
+  <si>
+    <t>配置中心接口与分组管理</t>
+  </si>
+  <si>
+    <t>分组可读可改；敏感配置加密存储</t>
+  </si>
+  <si>
+    <t>实现 7 组配置的读取、保存、整批校验与变更审计</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P1.10；预估：1d；验收：含对配置项展示与校验体验的修复</t>
+  </si>
+  <si>
+    <t>敏感配置安全展示与前端配置中心</t>
+  </si>
+  <si>
+    <t>实现敏感项只写不读、读接口脱敏、页面不回显与配置中心完整页面</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.9；预估：1d；验收：页面、日志与接口均无 api_key、Secret 值与 kubeconfig 明文；说明：含左栏+全宽布局与首屏展示修复</t>
+  </si>
+  <si>
+    <t>用户、角色与授权管理后端</t>
+  </si>
+  <si>
+    <t>可建用户并分配角色；按 namespace 授权，零权限起步；内置 admin 受保护</t>
+  </si>
+  <si>
+    <t>实现用户/角色增删改查、namespace 授权与令牌管理</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P1.5, P1.6；预估：1d</t>
+  </si>
+  <si>
+    <t>用户与权限管理页面</t>
+  </si>
+  <si>
+    <t>授权流程可完整操作；未授权操作后端仍拦截</t>
+  </si>
+  <si>
+    <t>未开始</t>
+  </si>
+  <si>
+    <t>实现用户列表、角色权限矩阵、namespace 授权与销毁能力委派页面</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.11, P2.3；预估：1d</t>
+  </si>
+  <si>
+    <t>平台能力测试与安全红线回归</t>
+  </si>
+  <si>
+    <t>补齐集群、Skill、配置、用户模块测试与敏感数据隔离回归</t>
+  </si>
+  <si>
+    <t>里程碑：M3；依赖：P3.12；预估：0.5d；验收：相关包测试全绿；Secret/kubeconfig/API key 隔离用例通过</t>
+  </si>
+  <si>
+    <t>待审批列表接口与页面</t>
+  </si>
+  <si>
+    <t>P4 治理（审批/审计）</t>
+  </si>
+  <si>
+    <t>实现待审批列表、筛选与分页</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P1.2；预估：0.5d；验收：与审批存储数据一致；页面可读风险、资源、集群</t>
+  </si>
+  <si>
+    <t>审批详情与决策依据展示</t>
+  </si>
+  <si>
+    <t>一个审批能完整解释「为什么需要审批」</t>
+  </si>
+  <si>
+    <t>实现审批详情面板：风险、工具、参数摘要、资源、授权、关联审计</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P4.1, P1.11；预估：1d</t>
+  </si>
+  <si>
+    <t>批准/拒绝与 Agent 暂停恢复</t>
+  </si>
+  <si>
+    <t>实现审批通过、拒绝接口与 Agent 暂停/恢复</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P1.8, P4.1；预估：0.5d；验收：拒绝后 Agent 可重新规划；审批结果回写审计</t>
+  </si>
+  <si>
+    <t>审批历史与决策解释</t>
+  </si>
+  <si>
+    <t>实现审批历史列表与决策原因（自动/需审批/拒绝）展示</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P4.3；预估：0.5d；验收：每条审批可展示风险、模式、授权与命中原因</t>
+  </si>
+  <si>
+    <t>审批策略配置（含自动审批白名单）</t>
+  </si>
+  <si>
+    <t>白名单外写操作至少需自确认；高危与 Shell 永不自动；配置即时生效</t>
+  </si>
+  <si>
+    <t>实现严格/智能模式、风险与 Shell 策略、禁止操作、Secret 策略与自动审批白名单配置</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P1.10, P4.4；预估：1d</t>
+  </si>
+  <si>
+    <t>授权模型与集群权限同步</t>
+  </si>
+  <si>
+    <t>授权删除或过期即回收集群权限；未授权确定性拒绝</t>
+  </si>
+  <si>
+    <t>实现平台授权为准、集群权限派生，含对账回收、撤销即删与执行前权限校验</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P1.2, P4.5；预估：1d</t>
+  </si>
+  <si>
+    <t>审计中心页面与时间线</t>
+  </si>
+  <si>
+    <t>可完整回放一次 Agent 操作链路</t>
+  </si>
+  <si>
+    <t>实现审计查询接口与按用户/集群/会话/事件/时间筛选的时间线</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P1.11；预估：1d</t>
+  </si>
+  <si>
+    <t>审批、授权与审计一致性与越权测试</t>
+  </si>
+  <si>
+    <t>专项用例全绿；越权与不一致场景有回归保护</t>
+  </si>
+  <si>
+    <t>覆盖越权、授权一致性、审批与审计对账的专项测试</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P4.6, P4.7；预估：1d</t>
+  </si>
+  <si>
+    <t>可观测性关联信息回填</t>
+  </si>
+  <si>
+    <t>补齐审批、执行与审计链路中的关联标识与可观测信息</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P4.7；预估：0.5d；验收：同一操作可在审批、审计与日志间关联追踪</t>
+  </si>
+  <si>
+    <t>多 Agent 注册与审批 Agent</t>
+  </si>
+  <si>
+    <t>审批 Agent 可执行自动审批决策并留痕；不突破安全边界</t>
+  </si>
+  <si>
+    <t>建立 Agent 注册表，落地首个审批 Agent 与能力/策略绑定</t>
+  </si>
+  <si>
+    <t>里程碑：M4；依赖：P4.5；预估：1.5d</t>
+  </si>
+  <si>
+    <t>会话摘要生成服务</t>
+  </si>
+  <si>
+    <t>P5 记忆与数据保留</t>
+  </si>
+  <si>
+    <t>摘要不含 Secret/kubeconfig 与未脱敏日志</t>
+  </si>
+  <si>
+    <t>会话结束后生成脱敏摘要并进入记忆候选</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P1.8；预估：1.5d</t>
+  </si>
+  <si>
+    <t>记忆存储与作用域策略</t>
+  </si>
+  <si>
+    <t>不同作用域查询隔离正确</t>
+  </si>
+  <si>
+    <t>实现用户/命名空间/集群三类作用域与可配置策略</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P1.2, P1.10；预估：1d</t>
+  </si>
+  <si>
+    <t>长期记忆召回与注入</t>
+  </si>
+  <si>
+    <t>仅注入允许内容；安全红线有回归用例</t>
+  </si>
+  <si>
+    <t>Agent 启动时按策略召回相关长期记忆并注入上下文</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P5.2；预估：1d</t>
+  </si>
+  <si>
+    <t>数据保留策略模型与配置</t>
+  </si>
+  <si>
+    <t>实现会话/审计/扫描/Skill 运行/记忆/配置历史/凭据的保留策略</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P1.10；预估：0.5d；验收：每类数据可独立配置开关、保留天数、数量上限与清理方式</t>
+  </si>
+  <si>
+    <t>数据保留清理调度器</t>
+  </si>
+  <si>
+    <t>可跑通各类数据清理，结果可审计</t>
+  </si>
+  <si>
+    <t>实现后台调度器按频率执行清理与归档</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P5.4；预估：1d</t>
+  </si>
+  <si>
+    <t>归档、删除动作与页面</t>
+  </si>
+  <si>
+    <t>归档不破坏业务；恢复逻辑可验证</t>
+  </si>
+  <si>
+    <t>实现数据归档、恢复与清理页面</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P5.5；预估：1d</t>
+  </si>
+  <si>
+    <t>记忆与保留策略配置页面</t>
+  </si>
+  <si>
+    <t>在配置中心实现记忆与数据保留分组页面</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P3.9, P5.5；预估：0.5d；验收：页面保存即生效；测试数据不会被误删</t>
+  </si>
+  <si>
+    <t>记忆与保留安全测试</t>
+  </si>
+  <si>
+    <t>覆盖摘要、召回、清理全链路测试</t>
+  </si>
+  <si>
+    <t>里程碑：M5；依赖：P5.6；预估：0.5d；验收：全程无 Secret/kubeconfig 明文；误删场景有保护</t>
+  </si>
+  <si>
+    <t>平台主进程启动装配与静态资源开关</t>
+  </si>
+  <si>
+    <t>P6 生产与准出</t>
+  </si>
+  <si>
+    <t>本地单进程与容器内均可完成迁移、引导与健康检查；可切换内嵌/关闭静态资源</t>
+  </si>
+  <si>
+    <t>完成 server 启动参数、配置与数据库注入、首次管理员引导、健康检查，以及前端静态资源托管开关</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P1.12；预估：1d</t>
+  </si>
+  <si>
+    <t>Kubernetes 部署清单（一体化 + 前后端分离）</t>
+  </si>
+  <si>
+    <t>两种形态均可部署访问；默认只读权限，写权限显式开启；数据持久化；单副本</t>
+  </si>
+  <si>
+    <t>提供一体化单 Deployment 清单，以及前后端分离的双 Deployment、双 Service 与按路径分流 Ingress</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P1.12, P6.1；预估：1.5d</t>
+  </si>
+  <si>
+    <t>镜像内写执行方案</t>
+  </si>
+  <si>
+    <t>不新增 Shell 写通道；安全门禁与执行边界保持唯一</t>
+  </si>
+  <si>
+    <t>确定并落地镜像内统一写执行方式（client-go 或固定版本 kubectl）</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.2；预估：1.5d</t>
+  </si>
+  <si>
+    <t>一键安装脚本</t>
+  </si>
+  <si>
+    <t>可一键部署到 K8s，脚本幂等可重跑</t>
+  </si>
+  <si>
+    <t>提供 deploy/install.sh，支持镜像、命名空间、存储类、域名、写权限与管理员密码参数</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.2；预估：1d</t>
+  </si>
+  <si>
+    <t>数据库持久化与迁移部署</t>
+  </si>
+  <si>
+    <t>用 Job 或初始化容器执行迁移，数据用 PVC 或 MySQL 承载</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.2；预估：0.5d；验收：重启不丢数据；迁移失败阻塞启动并可从日志定位</t>
+  </si>
+  <si>
+    <t>安全红线专项测试</t>
+  </si>
+  <si>
+    <t>专项测试全绿，不通过不准出</t>
+  </si>
+  <si>
+    <t>覆盖 Secret/kubeconfig 隔离、接口鉴权、实时流鉴权与角色越权</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P1.5, P1.11, P5.8；预估：1d</t>
+  </si>
+  <si>
+    <t>端到端冒烟（一体化与前后端分离）</t>
+  </si>
+  <si>
+    <t>三条路径均可跑通登录→集群→对话→审批→创建→审计；分离形态下实时流无缓冲延迟</t>
+  </si>
+  <si>
+    <t>覆盖本地单进程、一体化 K8s 与前后端分离 K8s 三条路径的完整业务冒烟</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.1, P6.2, P6.4；预估：2d</t>
+  </si>
+  <si>
+    <t>三期数据迁移测试</t>
+  </si>
+  <si>
+    <t>无提示丢失用例通过；不可迁移数据有显式报告</t>
+  </si>
+  <si>
+    <t>验证旧配置、会话、审计、Skill 与报告的全量导入</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P1.12, P6.5；预估：1d</t>
+  </si>
+  <si>
+    <t>文档、版本与发布准出</t>
+  </si>
+  <si>
+    <t>术语、版本与能力口径一致；发布命令可直接执行</t>
+  </si>
+  <si>
+    <t>统一更新变更记录、版本规则、安装部署、技术手册、项目状态与发布说明</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.7；预估：1d</t>
+  </si>
+  <si>
+    <t>全量门禁与打包</t>
+  </si>
+  <si>
+    <t>执行后端测试、静态检查、架构测试、前端 lint/测试/构建与既有打包脚本</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.9；预估：0.5d；验收：全部通过；产物版本信息注入正确</t>
+  </si>
+  <si>
+    <t>一体化形态：前端资源内嵌与同源交付</t>
+  </si>
+  <si>
+    <t>单端口即可访问页面与接口；刷新子路由不 404；不再依赖开发服务器</t>
+  </si>
+  <si>
+    <t>构建时把前端产物内嵌进二进制，实现前端路由回退、缓存策略与 /api/v1 同源单端口</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.1；预估：1d</t>
+  </si>
+  <si>
+    <t>平台配置面收口（静态配置 + 动态配置分离）</t>
+  </si>
+  <si>
+    <t>动态配置只在数据库维护，配置文件不再出现；模板有测试锁定；敏感值只从密钥注入</t>
+  </si>
+  <si>
+    <t>接入静态启动配置，收敛配置模板；运行时统一从数据库读取动态配置；补齐改密与配置中心布局</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.1；预估：1.5d</t>
+  </si>
+  <si>
+    <t>前后端分离形态：独立前端部署</t>
+  </si>
+  <si>
+    <t>前后端可独立升级与回滚；同域访问无跨域；实时流正常；未拆服务、未改业务逻辑</t>
+  </si>
+  <si>
+    <t>提供前端静态镜像（含路由回退与缓存）、后端纯接口开关、双部署清单与同域路径分流</t>
+  </si>
+  <si>
+    <t>里程碑：M6；依赖：P6.1, P6.2, P6.11；预估：1d</t>
+  </si>
+  <si>
+    <t>前端体验地基（设计令牌 / 亮暗主题 / 防闪烁）</t>
+  </si>
+  <si>
+    <t>P7 Web Shell 体验优化</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>刷新无闪烁；亮暗两套无写死颜色残留；无系统白色滚动条</t>
+  </si>
+  <si>
+    <t>设计令牌（亮/暗两套）、data-theme 与 html.dark 同步切换、主题模式 light|dark|system（默认 dark、持久化、内联脚本防闪烁）、自定义纤细滚动条、海拔体系与行高 1.6、空状态引导</t>
+  </si>
+  <si>
+    <t>里程碑：M7；依赖：纯前端；预估：2.5d；验收：单测覆盖默认 dark / system 跟随 / 切换持久化</t>
+  </si>
+  <si>
+    <t>聊天交互（智能跟随 / Run Bar / 输入区常驻）</t>
+  </si>
+  <si>
+    <t>上滑暂停跟随、回到底部恢复；点阶段准确定位；长会话输入框常驻</t>
+  </si>
+  <si>
+    <t>智能跟随与回到底部（阈值 24px）、Run Bar 阶段高亮与定位（scroll-margin-top 避让 sticky）、输入区精致化、安全提示降级、双栏高度链（输入区常驻）</t>
+  </si>
+  <si>
+    <t>里程碑：M7；依赖：P7.1；预估：2d；验收：40 条会话 + 长消息无页面级滚动</t>
+  </si>
+  <si>
+    <t>视觉收口（Markdown 报告 / 登录页主题化）</t>
+  </si>
+  <si>
+    <t>报告亮暗两套正常；登录页无原文案且主题完整</t>
+  </si>
+  <si>
+    <t>Markdown 报告主题化（标题/表格/代码块/引用/行内代码、长代码块折叠）、登录页文案替换、背景沿用既有 Canvas 粒子并补 dispose 清理</t>
+  </si>
+  <si>
+    <t>里程碑：M7；依赖：P7.1；预估：1.5d；验收：prefers-reduced-motion 降级；无空引用报错</t>
+  </si>
+  <si>
+    <t>工具卡与 tool_result 契约（同源摘要）</t>
+  </si>
+  <si>
+    <t>chat 与刷新后结果一致；头部摘要一致；耗时/风险可读</t>
+  </si>
+  <si>
+    <t>后端 tool_result 事件与落库同源（summary/displayType 后端计算）、消息补 durationMs/risk；前端结构化渲染（表格分页/虚拟滚动、Raw 折叠、运行中/错误默认展开、报告后自动折叠、手动状态持久化、展开/折叠全部）</t>
+  </si>
+  <si>
+    <t>里程碑：M7；依赖：ADR-034；预估：2.5d；验收："成功 · N pods · 320ms" 刷新后仍成立</t>
+  </si>
+  <si>
+    <t>会话列表（自动标题 / 搜索 / 置顶 / 导出）</t>
+  </si>
+  <si>
+    <t>置顶排最前且刷新保持；重命名/删除有确认与 Toast；导出无敏感值</t>
+  </si>
+  <si>
+    <t>标题自动提取（列表接口返回时计算）、状态胶囊右上、搜索框、三点菜单（重命名/置顶/导出 Markdown/删除）、置顶分组分隔带、移动端抽屉、折叠开关、导出走 Blob 下载</t>
+  </si>
+  <si>
+    <t>里程碑：M7；依赖：置顶需后端字段；预估：2d；验收：导出的 .md 按时序含提问/思考/工具/报告且无敏感值</t>
+  </si>
+  <si>
     <t>P0.1</t>
   </si>
   <si>
     <t>四期需求与范围复审、决策签收 D-01~D-18</t>
   </si>
   <si>
+    <t>规格与设计基线</t>
+  </si>
+  <si>
     <t>本文档 §2、需求 v1.3 决策状态回写</t>
   </si>
   <si>
-    <t>里程碑：M1；依赖：需求 v1.3；规模：M；预估：0.5d；验收：D-06 等推荐值有结论并回写文档；D-15~D-18 审批/授权新增决策纳入并在需求文档标注</t>
+    <t>里程碑：M1；依赖：需求 v1.3；规模：M；
+预估：0.5d；验收：D-06 等推荐值有结论
+并回写文档；D-15~D-18 审批/授权新增决
+策纳入并在需求文档标注</t>
   </si>
   <si>
     <t>P0.2</t>
@@ -412,7 +1334,8 @@
     <t>docs/API_V4.md：认证、集群、Skill、配置、用户、Approval、Audit、Chat SSE 与通用错误/分页</t>
   </si>
   <si>
-    <t>里程碑：M1；依赖：P0.1；规模：L；预估：1d；验收：前端可基于该 Contract mock 开发；错误码与权限码定义完整</t>
+    <t>里程碑：M1；依赖：P0.1；规模：L；
+预估：1d；验收：前端可基于该 Contract mock 开发；错误码与权限码定义完整</t>
   </si>
   <si>
     <t>P0.3</t>
@@ -424,7 +1347,9 @@
     <t>internal/store 接口草案、SQLite/MySQL schema 与版本迁移策略</t>
   </si>
   <si>
-    <t>里程碑：M1；依赖：P0.1；规模：L；预估：1d；验收：业务层依赖接口；migration 可升级，不无提示丢数据</t>
+    <t>里程碑：M1；依赖：P0.1；规模：L；
+预估：1d；验收：业务层依赖接口；
+migration 可升级，不无提示丢数据</t>
   </si>
   <si>
     <t>P0.4</t>
@@ -436,19 +1361,18 @@
     <t>docs/SSE_EVENT_V4.md：session/turn/step 事件 + 三期 answer-delta/reasoning-delta/tool-call/tool-result 映射</t>
   </si>
   <si>
-    <t>里程碑：M1；依赖：P0.2；规模：M；预估：0.5d；验收：每个事件必有 session_id/turn_id/step_id/timestamp/event_type；迁移映射可用</t>
+    <t>里程碑：M1；依赖：P0.2；规模：M；
+预估：0.5d；验收：每个事件必有 session_id/turn_id/step_id/timestamp/event_type；迁移映射可用</t>
   </si>
   <si>
     <t>P0.5</t>
   </si>
   <si>
-    <t>前端信息架构与目录规范</t>
-  </si>
-  <si>
     <t>web/ 目录、页面侧栏、权限前端三视图（Route/Component/Button）设计</t>
   </si>
   <si>
-    <t>里程碑：M1；依赖：P0.2；规模：M；预估：0.5d；验收：一级路由与 v1.3 §10/§11 对应；侧栏按 D-15 三组分栏，Admin 入右上角 User Menu；权限仅 UX，后端强校验原则写明</t>
+    <t>里程碑：M1；依赖：P0.2；规模：M；
+预估：0.5d；验收：一级路由与 v1.3 §10/§11 对应；侧栏按 D-15 三组分栏，Admin 入右上角 User Menu；权限仅 UX，后端强校验原则写明</t>
   </si>
   <si>
     <t>P0.6</t>
@@ -460,7 +1384,8 @@
     <t>docs/MIGRATION_V4.md：旧 config.yaml、旧 Skill、旧 Session/Chat、旧 Approval、旧 Report、旧配置目录</t>
   </si>
   <si>
-    <t>里程碑：M1；依赖：P0.1；规模：M；预估：0.5d；验收：每个数据源都有迁移/显式拒绝两条结论；验收用例可追踪</t>
+    <t>里程碑：M1；依赖：P0.1；规模：M；
+预估：0.5d；验收：每个数据源都有迁移/显式拒绝两条结论；验收用例可追踪</t>
   </si>
   <si>
     <t>P1.0</t>
@@ -478,13 +1403,11 @@
     <t>Vite + Vue3 + TS 工程骨架</t>
   </si>
   <si>
-    <t>进行中</t>
-  </si>
-  <si>
     <t>web/ 工程、package.json、lint/format、CI build 步骤</t>
   </si>
   <si>
-    <t>里程碑：M1；依赖：P0.5；规模：L；预估：1d；验收：`npm run build` 与 `npm run lint` 通过；基础路由可访问</t>
+    <t>里程碑：M1；依赖：P0.5；规模：L；
+预估：1d；验收：`npm run build` 与 `npm run lint` 通过；基础路由可访问</t>
   </si>
   <si>
     <t>P1.2</t>
@@ -493,9 +1416,6 @@
     <t>Store 接口与 SQLite 驱动</t>
   </si>
   <si>
-    <t>未开始</t>
-  </si>
-  <si>
     <t>internal/store：User/Session/Role/Audit/Settings/Skill/Approval/Memory/Retention/Cluster/Credential Store；SQLite 实现与迁移</t>
   </si>
   <si>
@@ -517,9 +1437,6 @@
     <t>P1.4</t>
   </si>
   <si>
-    <t>HTTP 基础中间件</t>
-  </si>
-  <si>
     <t>request_id、统一 error envelope、分页、CORS、认证占位</t>
   </si>
   <si>
@@ -649,9 +1566,6 @@
     <t>P2.2</t>
   </si>
   <si>
-    <t>登录页与前端路由守卫</t>
-  </si>
-  <si>
     <t>/login、/app/* 路由守卫、401 跳登录</t>
   </si>
   <si>
@@ -673,9 +1587,6 @@
     <t>P2.4</t>
   </si>
   <si>
-    <t>会话列表与历史会话加载</t>
-  </si>
-  <si>
     <t>ConversationList、创建/选择/删除会话</t>
   </si>
   <si>
@@ -769,9 +1680,6 @@
     <t>P2.12</t>
   </si>
   <si>
-    <t>前端测试与构建门禁</t>
-  </si>
-  <si>
     <t>web/src/**/*.test.ts、E2E 冒烟、lint/build</t>
   </si>
   <si>
@@ -985,9 +1893,6 @@
     <t>P4.4</t>
   </si>
   <si>
-    <t>审批历史与决策解释</t>
-  </si>
-  <si>
     <t>History 列表、Decision AUTO/REQUIRE_APPROVAL/DENY 说明</t>
   </si>
   <si>
@@ -1093,9 +1998,6 @@
     <t>P5.3</t>
   </si>
   <si>
-    <t>长期记忆召回与注入</t>
-  </si>
-  <si>
     <t>Agent 启动时读取相关长期记忆，按 Policy 注入上下文</t>
   </si>
   <si>
@@ -1213,9 +2115,6 @@
     <t>P6.5</t>
   </si>
   <si>
-    <t>数据库持久化与迁移部署</t>
-  </si>
-  <si>
     <t>K8s Job/initContainer 执行 migration；PVC 挂载 SQLite 或 MySQL DSN</t>
   </si>
   <si>
@@ -1249,9 +2148,6 @@
     <t>P6.8</t>
   </si>
   <si>
-    <t>三期数据迁移测试</t>
-  </si>
-  <si>
     <t>旧 config/session/audit/skill/report 全量导入测试</t>
   </si>
   <si>
@@ -1271,9 +2167,6 @@
   </si>
   <si>
     <t>P6.10</t>
-  </si>
-  <si>
-    <t>全量门禁与打包</t>
   </si>
   <si>
     <t>`go test ./...`、`go vet ./...`、tests/arch、前端 lint/build、既有打包脚本</t>
@@ -1292,7 +2185,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1311,6 +2204,18 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1459,7 +2364,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1481,6 +2386,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1812,58 +2729,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
@@ -1875,74 +2786,80 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1951,6 +2868,41 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1970,9 +2922,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2337,1060 +3286,1060 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10">
-      <c r="A3" s="4">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10">
-      <c r="A4" s="4">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10">
-      <c r="A5" s="4">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10">
-      <c r="A6" s="4">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="17"/>
+      <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="18" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10">
-      <c r="A7" s="4">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="18" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10">
-      <c r="A8" s="4">
+      <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="18" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10">
-      <c r="A9" s="4">
+      <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="18" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10">
-      <c r="A10" s="4">
+      <c r="A10" s="17">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="18" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10">
-      <c r="A11" s="4">
+      <c r="A11" s="17">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10">
-      <c r="A12" s="4">
+      <c r="A12" s="17">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="18" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10">
-      <c r="A13" s="4">
+      <c r="A13" s="17">
         <v>11</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10">
-      <c r="A14" s="4">
+      <c r="A14" s="17">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="5" t="s">
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10">
-      <c r="A15" s="4">
+      <c r="A15" s="17">
         <v>13</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="5" t="s">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="18" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10">
-      <c r="A16" s="4">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="17">
+        <v>14</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="17"/>
+      <c r="E16" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="5" t="s">
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="18" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10">
-      <c r="A17" s="4">
+      <c r="A17" s="17">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="5" t="s">
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="18" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10">
-      <c r="A18" s="4">
+      <c r="A18" s="17">
         <v>16</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
+      <c r="D18" s="17"/>
+      <c r="E18" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="5" t="s">
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="18" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10">
-      <c r="A19" s="4">
+      <c r="A19" s="17">
         <v>17</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="5" t="s">
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="18" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10">
-      <c r="A20" s="4">
+      <c r="A20" s="17">
         <v>18</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4" t="s">
+      <c r="D20" s="17"/>
+      <c r="E20" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="5" t="s">
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10">
-      <c r="A21" s="4">
+      <c r="A21" s="17">
         <v>19</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="18" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10">
-      <c r="A22" s="4">
+      <c r="A22" s="17">
         <v>20</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="5" t="s">
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10">
-      <c r="A23" s="4">
+      <c r="A23" s="17">
         <v>21</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="5" t="s">
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10">
-      <c r="A24" s="4">
+      <c r="A24" s="17">
         <v>22</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
+      <c r="D24" s="17"/>
+      <c r="E24" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="5" t="s">
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10">
-      <c r="A25" s="4">
+      <c r="A25" s="17">
         <v>23</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
+      <c r="D25" s="17"/>
+      <c r="E25" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="5" t="s">
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10">
-      <c r="A26" s="4">
+      <c r="A26" s="17">
         <v>24</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
+      <c r="D26" s="17"/>
+      <c r="E26" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="5" t="s">
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10">
-      <c r="A27" s="6">
+      <c r="A27" s="19">
         <v>25</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="19"/>
+      <c r="E27" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="21">
         <v>46286</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="21">
         <v>46288</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="7" t="s">
+      <c r="H27" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="20" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:10">
-      <c r="A28" s="4">
+      <c r="A28" s="17">
         <v>26</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="22">
         <v>46289</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="22">
         <v>46290</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="5" t="s">
+      <c r="H28" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:10">
-      <c r="A29" s="4">
+      <c r="A29" s="17">
         <v>27</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4" t="s">
+      <c r="D29" s="17"/>
+      <c r="E29" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="22">
         <v>46293</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="5" t="s">
+      <c r="H29" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:10">
-      <c r="A30" s="4">
+      <c r="A30" s="17">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4" t="s">
+      <c r="D30" s="17"/>
+      <c r="E30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="22">
         <v>46293</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="22">
         <v>46294</v>
       </c>
-      <c r="H30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="5" t="s">
+      <c r="H30" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="18" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:10">
-      <c r="A31" s="4">
+      <c r="A31" s="17">
         <v>29</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4" t="s">
+      <c r="D31" s="17"/>
+      <c r="E31" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="22">
         <v>46307</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="22">
         <v>46307</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="5" t="s">
+      <c r="H31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:10">
-      <c r="A32" s="4">
+      <c r="A32" s="17">
         <v>30</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="22">
         <v>46303</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="22">
         <v>46304</v>
       </c>
-      <c r="H32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="5" t="s">
+      <c r="H32" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="18" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:10">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:10">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="1:10">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:10">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:10">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:10">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:10">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:10">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:10">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:10">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="1:10">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="1:10">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="1:10">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="1:10">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="1:10">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="1:10">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="1:10">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="1:10">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="1:10">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="1:10">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="1:10">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3405,23 +4354,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="39.6991150442478" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.2212389380531" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.2920353982301" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.8230088495575" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.1504424778761" style="1" customWidth="1"/>
-    <col min="10" max="10" width="43.6106194690265" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.9557522123894" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" customWidth="1"/>
+    <col min="9" max="9" width="58" style="1" customWidth="1"/>
+    <col min="10" max="10" width="52" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1" spans="1:10">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" ht="14.65" customHeight="1" spans="1:10">
+    <row r="1" ht="32" customHeight="1" spans="1:10">
+      <c r="A1" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3453,1706 +4405,2171 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" ht="64" customHeight="1" spans="1:10">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1" spans="1:10">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1" spans="1:10">
+      <c r="A5" s="11">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1" spans="1:10">
+      <c r="A6" s="11">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1" spans="1:10">
+      <c r="A7" s="11">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1" spans="1:10">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1" spans="1:10">
+      <c r="A9" s="14">
+        <v>7</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1" spans="1:10">
+      <c r="A10" s="11">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1" spans="1:10">
+      <c r="A11" s="11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1" spans="1:10">
+      <c r="A12" s="11">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1" spans="1:10">
+      <c r="A13" s="11">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1" spans="1:10">
+      <c r="A14" s="11">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B14" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1" spans="1:10">
+      <c r="A15" s="11">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1" spans="1:10">
+      <c r="A16" s="11">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1" spans="1:10">
+      <c r="A17" s="11">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1" spans="1:10">
+      <c r="A18" s="11">
+        <v>16</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1" spans="1:10">
+      <c r="A19" s="11">
+        <v>17</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1" spans="1:10">
+      <c r="A20" s="11">
+        <v>18</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1" spans="1:10">
+      <c r="A21" s="11">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>124</v>
-      </c>
-      <c r="J4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="s">
-        <v>128</v>
-      </c>
-      <c r="J5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1" spans="1:10">
+      <c r="A22" s="11">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1" spans="1:10">
+      <c r="A23" s="11">
+        <v>21</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" ht="64" customHeight="1" spans="1:10">
+      <c r="A24" s="11">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1" spans="1:10">
+      <c r="A25" s="11">
+        <v>23</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" ht="64" customHeight="1" spans="1:10">
+      <c r="A26" s="11">
+        <v>24</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1" spans="1:10">
+      <c r="A27" s="11">
+        <v>25</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" t="s">
-        <v>136</v>
-      </c>
-      <c r="J7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1" spans="1:10">
+      <c r="A28" s="11">
+        <v>26</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1" spans="1:10">
+      <c r="A29" s="11">
+        <v>27</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>140</v>
-      </c>
-      <c r="J8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" t="s">
-        <v>148</v>
-      </c>
-      <c r="J10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s">
-        <v>152</v>
-      </c>
-      <c r="I11" t="s">
-        <v>153</v>
-      </c>
-      <c r="J11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" t="s">
-        <v>157</v>
-      </c>
-      <c r="J12" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1" spans="1:10">
+      <c r="A30" s="11">
+        <v>28</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1" spans="1:10">
+      <c r="A31" s="11">
+        <v>29</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H13" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" t="s">
-        <v>161</v>
-      </c>
-      <c r="J13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B14" t="s">
-        <v>164</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1" spans="1:10">
+      <c r="A32" s="11">
+        <v>30</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H15" t="s">
-        <v>152</v>
-      </c>
-      <c r="I15" t="s">
-        <v>169</v>
-      </c>
-      <c r="J15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" t="s">
-        <v>152</v>
-      </c>
-      <c r="I16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J16" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I17" t="s">
-        <v>177</v>
-      </c>
-      <c r="J17" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>179</v>
-      </c>
-      <c r="B18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" t="s">
-        <v>181</v>
-      </c>
-      <c r="J18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" t="s">
-        <v>185</v>
-      </c>
-      <c r="J19" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1" spans="1:10">
+      <c r="A33" s="11">
+        <v>31</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D33" s="11"/>
+      <c r="E33" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1" spans="1:10">
+      <c r="A34" s="11">
+        <v>32</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H20" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" t="s">
-        <v>189</v>
-      </c>
-      <c r="J20" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B21" t="s">
-        <v>192</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" t="s">
-        <v>193</v>
-      </c>
-      <c r="J21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1" spans="1:10">
+      <c r="A35" s="11">
+        <v>33</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1" spans="1:10">
+      <c r="A36" s="11">
+        <v>34</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1" spans="1:10">
+      <c r="A37" s="11">
+        <v>35</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H22" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" t="s">
-        <v>197</v>
-      </c>
-      <c r="J22" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>199</v>
-      </c>
-      <c r="B23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1" spans="1:10">
+      <c r="A38" s="11">
+        <v>36</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1" spans="1:10">
+      <c r="A39" s="11">
+        <v>37</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1" spans="1:10">
+      <c r="A40" s="11">
+        <v>38</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1" spans="1:10">
+      <c r="A41" s="11">
+        <v>39</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H23" t="s">
-        <v>152</v>
-      </c>
-      <c r="I23" t="s">
-        <v>201</v>
-      </c>
-      <c r="J23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B24" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1" spans="1:10">
+      <c r="A42" s="11">
+        <v>40</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1" spans="1:10">
+      <c r="A43" s="11">
+        <v>41</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1" spans="1:10">
+      <c r="A44" s="11">
+        <v>42</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H24" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" t="s">
-        <v>205</v>
-      </c>
-      <c r="J24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>207</v>
-      </c>
-      <c r="B25" t="s">
-        <v>208</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1" spans="1:10">
+      <c r="A45" s="11">
+        <v>43</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1" spans="1:10">
+      <c r="A46" s="11">
+        <v>44</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1" spans="1:10">
+      <c r="A47" s="11">
+        <v>45</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H25" t="s">
-        <v>152</v>
-      </c>
-      <c r="I25" t="s">
-        <v>209</v>
-      </c>
-      <c r="J25" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>211</v>
-      </c>
-      <c r="B26" t="s">
-        <v>212</v>
-      </c>
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1" spans="1:10">
+      <c r="A48" s="11">
+        <v>46</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H26" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" t="s">
-        <v>213</v>
-      </c>
-      <c r="J26" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>215</v>
-      </c>
-      <c r="B27" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" t="s">
-        <v>152</v>
-      </c>
-      <c r="I27" t="s">
-        <v>217</v>
-      </c>
-      <c r="J27" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>219</v>
-      </c>
-      <c r="B28" t="s">
-        <v>220</v>
-      </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1" spans="1:10">
+      <c r="A49" s="11">
+        <v>47</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1" spans="1:10">
+      <c r="A50" s="11">
+        <v>48</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H28" t="s">
-        <v>152</v>
-      </c>
-      <c r="I28" t="s">
-        <v>221</v>
-      </c>
-      <c r="J28" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>223</v>
-      </c>
-      <c r="B29" t="s">
-        <v>224</v>
-      </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" t="s">
-        <v>152</v>
-      </c>
-      <c r="I29" t="s">
-        <v>225</v>
-      </c>
-      <c r="J29" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" t="s">
-        <v>228</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="51" ht="64" customHeight="1" spans="1:10">
+      <c r="A51" s="11">
+        <v>49</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H30" t="s">
-        <v>152</v>
-      </c>
-      <c r="I30" t="s">
-        <v>229</v>
-      </c>
-      <c r="J30" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>231</v>
-      </c>
-      <c r="B31" t="s">
-        <v>232</v>
-      </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" t="s">
-        <v>152</v>
-      </c>
-      <c r="I31" t="s">
-        <v>233</v>
-      </c>
-      <c r="J31" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" t="s">
-        <v>235</v>
-      </c>
-      <c r="B32" t="s">
-        <v>236</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="52" ht="64" customHeight="1" spans="1:10">
+      <c r="A52" s="11">
+        <v>50</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" ht="64" customHeight="1" spans="1:10">
+      <c r="A53" s="11">
+        <v>51</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54" ht="64" customHeight="1" spans="1:10">
+      <c r="A54" s="11">
         <v>52</v>
       </c>
-      <c r="H32" t="s">
-        <v>152</v>
-      </c>
-      <c r="I32" t="s">
-        <v>237</v>
-      </c>
-      <c r="J32" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>239</v>
-      </c>
-      <c r="B33" t="s">
-        <v>240</v>
-      </c>
-      <c r="C33" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="B54" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="55" ht="64" customHeight="1" spans="1:10">
+      <c r="A55" s="11">
+        <v>53</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1" spans="1:10">
+      <c r="A56" s="11">
+        <v>54</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H33" t="s">
-        <v>152</v>
-      </c>
-      <c r="I33" t="s">
-        <v>241</v>
-      </c>
-      <c r="J33" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>243</v>
-      </c>
-      <c r="B34" t="s">
-        <v>244</v>
-      </c>
-      <c r="C34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" t="s">
-        <v>152</v>
-      </c>
-      <c r="I34" t="s">
-        <v>245</v>
-      </c>
-      <c r="J34" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>247</v>
-      </c>
-      <c r="B35" t="s">
-        <v>248</v>
-      </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="57" ht="64" customHeight="1" spans="1:10">
+      <c r="A57" s="11">
+        <v>55</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="58" ht="64" customHeight="1" spans="1:10">
+      <c r="A58" s="11">
+        <v>56</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59" ht="64" customHeight="1" spans="1:10">
+      <c r="A59" s="11">
+        <v>57</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60" ht="64" customHeight="1" spans="1:10">
+      <c r="A60" s="11">
+        <v>58</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="61" ht="64" customHeight="1" spans="1:10">
+      <c r="A61" s="11">
+        <v>59</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H35" t="s">
-        <v>152</v>
-      </c>
-      <c r="I35" t="s">
-        <v>249</v>
-      </c>
-      <c r="J35" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>251</v>
-      </c>
-      <c r="B36" t="s">
-        <v>252</v>
-      </c>
-      <c r="C36" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" t="s">
-        <v>152</v>
-      </c>
-      <c r="I36" t="s">
-        <v>253</v>
-      </c>
-      <c r="J36" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>255</v>
-      </c>
-      <c r="B37" t="s">
-        <v>256</v>
-      </c>
-      <c r="C37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I37" t="s">
-        <v>257</v>
-      </c>
-      <c r="J37" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" t="s">
-        <v>259</v>
-      </c>
-      <c r="B38" t="s">
-        <v>260</v>
-      </c>
-      <c r="C38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="62" ht="64" customHeight="1" spans="1:10">
+      <c r="A62" s="11">
+        <v>60</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="63" ht="64" customHeight="1" spans="1:10">
+      <c r="A63" s="11">
+        <v>61</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="64" ht="64" customHeight="1" spans="1:10">
+      <c r="A64" s="11">
+        <v>62</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H38" t="s">
-        <v>152</v>
-      </c>
-      <c r="I38" t="s">
-        <v>261</v>
-      </c>
-      <c r="J38" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>263</v>
-      </c>
-      <c r="B39" t="s">
-        <v>264</v>
-      </c>
-      <c r="C39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I39" t="s">
-        <v>265</v>
-      </c>
-      <c r="J39" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>267</v>
-      </c>
-      <c r="B40" t="s">
-        <v>268</v>
-      </c>
-      <c r="C40" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" t="s">
-        <v>269</v>
-      </c>
-      <c r="J40" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" t="s">
-        <v>271</v>
-      </c>
-      <c r="B41" t="s">
-        <v>272</v>
-      </c>
-      <c r="C41" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41" t="s">
-        <v>273</v>
-      </c>
-      <c r="J41" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" t="s">
-        <v>275</v>
-      </c>
-      <c r="B42" t="s">
-        <v>276</v>
-      </c>
-      <c r="C42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="65" ht="64" customHeight="1" spans="1:15">
+      <c r="A65" s="11">
+        <v>63</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H42" t="s">
-        <v>152</v>
-      </c>
-      <c r="I42" t="s">
-        <v>277</v>
-      </c>
-      <c r="J42" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" t="s">
-        <v>279</v>
-      </c>
-      <c r="B43" t="s">
-        <v>280</v>
-      </c>
-      <c r="C43" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" t="s">
-        <v>13</v>
-      </c>
-      <c r="H43" t="s">
-        <v>152</v>
-      </c>
-      <c r="I43" t="s">
-        <v>281</v>
-      </c>
-      <c r="J43" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" t="s">
-        <v>283</v>
-      </c>
-      <c r="B44" t="s">
-        <v>284</v>
-      </c>
-      <c r="C44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" t="s">
-        <v>152</v>
-      </c>
-      <c r="I44" t="s">
-        <v>285</v>
-      </c>
-      <c r="J44" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>287</v>
-      </c>
-      <c r="B45" t="s">
-        <v>288</v>
-      </c>
-      <c r="C45" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="66" ht="64" customHeight="1" spans="1:15">
+      <c r="A66" s="11">
+        <v>64</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="67" ht="64" customHeight="1" spans="1:15">
+      <c r="A67" s="11">
+        <v>65</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="68" ht="64" customHeight="1" spans="1:15">
+      <c r="A68" s="11">
+        <v>66</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="J68" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="69" ht="64" customHeight="1" spans="1:15">
+      <c r="A69" s="11">
+        <v>67</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="70" ht="64" customHeight="1" spans="1:15">
+      <c r="A70" s="11">
+        <v>68</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H45" t="s">
-        <v>152</v>
-      </c>
-      <c r="I45" t="s">
-        <v>289</v>
-      </c>
-      <c r="J45" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" t="s">
-        <v>291</v>
-      </c>
-      <c r="B46" t="s">
-        <v>292</v>
-      </c>
-      <c r="C46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" t="s">
-        <v>152</v>
-      </c>
-      <c r="I46" t="s">
-        <v>293</v>
-      </c>
-      <c r="J46" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" t="s">
-        <v>295</v>
-      </c>
-      <c r="B47" t="s">
-        <v>296</v>
-      </c>
-      <c r="C47" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" t="s">
-        <v>152</v>
-      </c>
-      <c r="I47" t="s">
-        <v>297</v>
-      </c>
-      <c r="J47" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" t="s">
-        <v>299</v>
-      </c>
-      <c r="B48" t="s">
-        <v>300</v>
-      </c>
-      <c r="C48" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="71" ht="64" customHeight="1" spans="1:15">
+      <c r="A71" s="11">
+        <v>69</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="72" ht="64" customHeight="1" spans="1:15">
+      <c r="A72" s="11">
+        <v>70</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" ht="64" customHeight="1" spans="1:15">
+      <c r="A73" s="11">
+        <v>71</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="74" ht="64" customHeight="1" spans="1:15">
+      <c r="A74" s="11">
+        <v>72</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="75" ht="64" customHeight="1" spans="1:15">
+      <c r="A75" s="11">
+        <v>73</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H48" t="s">
-        <v>152</v>
-      </c>
-      <c r="I48" t="s">
-        <v>301</v>
-      </c>
-      <c r="J48" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" t="s">
-        <v>303</v>
-      </c>
-      <c r="B49" t="s">
-        <v>304</v>
-      </c>
-      <c r="C49" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" t="s">
-        <v>52</v>
-      </c>
-      <c r="H49" t="s">
-        <v>152</v>
-      </c>
-      <c r="I49" t="s">
-        <v>305</v>
-      </c>
-      <c r="J49" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>307</v>
-      </c>
-      <c r="B50" t="s">
-        <v>308</v>
-      </c>
-      <c r="C50" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" t="s">
-        <v>152</v>
-      </c>
-      <c r="I50" t="s">
-        <v>309</v>
-      </c>
-      <c r="J50" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>311</v>
-      </c>
-      <c r="B51" t="s">
-        <v>312</v>
-      </c>
-      <c r="C51" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" t="s">
-        <v>52</v>
-      </c>
-      <c r="H51" t="s">
-        <v>152</v>
-      </c>
-      <c r="I51" t="s">
-        <v>313</v>
-      </c>
-      <c r="J51" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" t="s">
-        <v>315</v>
-      </c>
-      <c r="B52" t="s">
-        <v>316</v>
-      </c>
-      <c r="C52" t="s">
-        <v>29</v>
-      </c>
-      <c r="E52" t="s">
-        <v>52</v>
-      </c>
-      <c r="H52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I52" t="s">
-        <v>317</v>
-      </c>
-      <c r="J52" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" t="s">
-        <v>319</v>
-      </c>
-      <c r="B53" t="s">
-        <v>320</v>
-      </c>
-      <c r="C53" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" t="s">
-        <v>152</v>
-      </c>
-      <c r="I53" t="s">
-        <v>321</v>
-      </c>
-      <c r="J53" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" t="s">
-        <v>323</v>
-      </c>
-      <c r="B54" t="s">
-        <v>324</v>
-      </c>
-      <c r="C54" t="s">
-        <v>29</v>
-      </c>
-      <c r="E54" t="s">
-        <v>13</v>
-      </c>
-      <c r="H54" t="s">
-        <v>152</v>
-      </c>
-      <c r="I54" t="s">
-        <v>325</v>
-      </c>
-      <c r="J54" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" t="s">
-        <v>327</v>
-      </c>
-      <c r="B55" t="s">
-        <v>328</v>
-      </c>
-      <c r="C55" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" t="s">
-        <v>13</v>
-      </c>
-      <c r="H55" t="s">
-        <v>152</v>
-      </c>
-      <c r="I55" t="s">
-        <v>329</v>
-      </c>
-      <c r="J55" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" t="s">
-        <v>331</v>
-      </c>
-      <c r="B56" t="s">
-        <v>332</v>
-      </c>
-      <c r="C56" t="s">
-        <v>29</v>
-      </c>
-      <c r="E56" t="s">
-        <v>13</v>
-      </c>
-      <c r="H56" t="s">
-        <v>152</v>
-      </c>
-      <c r="I56" t="s">
-        <v>333</v>
-      </c>
-      <c r="J56" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" t="s">
-        <v>335</v>
-      </c>
-      <c r="B57" t="s">
-        <v>336</v>
-      </c>
-      <c r="C57" t="s">
-        <v>29</v>
-      </c>
-      <c r="E57" t="s">
-        <v>52</v>
-      </c>
-      <c r="H57" t="s">
-        <v>152</v>
-      </c>
-      <c r="I57" t="s">
-        <v>337</v>
-      </c>
-      <c r="J57" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" t="s">
-        <v>339</v>
-      </c>
-      <c r="B58" t="s">
-        <v>340</v>
-      </c>
-      <c r="C58" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" t="s">
-        <v>152</v>
-      </c>
-      <c r="I58" t="s">
-        <v>341</v>
-      </c>
-      <c r="J58" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" t="s">
-        <v>343</v>
-      </c>
-      <c r="B59" t="s">
-        <v>344</v>
-      </c>
-      <c r="C59" t="s">
-        <v>33</v>
-      </c>
-      <c r="E59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" t="s">
-        <v>152</v>
-      </c>
-      <c r="I59" t="s">
-        <v>345</v>
-      </c>
-      <c r="J59" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" t="s">
-        <v>347</v>
-      </c>
-      <c r="B60" t="s">
-        <v>348</v>
-      </c>
-      <c r="C60" t="s">
-        <v>33</v>
-      </c>
-      <c r="E60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" t="s">
-        <v>152</v>
-      </c>
-      <c r="I60" t="s">
-        <v>349</v>
-      </c>
-      <c r="J60" t="s">
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="76" ht="64" customHeight="1" spans="1:15">
+      <c r="A76" s="11">
+        <v>74</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C76" s="11" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" t="s">
-        <v>351</v>
-      </c>
-      <c r="B61" t="s">
-        <v>352</v>
-      </c>
-      <c r="C61" t="s">
-        <v>33</v>
-      </c>
-      <c r="E61" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" t="s">
-        <v>152</v>
-      </c>
-      <c r="I61" t="s">
-        <v>353</v>
-      </c>
-      <c r="J61" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" t="s">
-        <v>355</v>
-      </c>
-      <c r="B62" t="s">
-        <v>356</v>
-      </c>
-      <c r="C62" t="s">
-        <v>33</v>
-      </c>
-      <c r="E62" t="s">
-        <v>52</v>
-      </c>
-      <c r="H62" t="s">
-        <v>152</v>
-      </c>
-      <c r="I62" t="s">
-        <v>357</v>
-      </c>
-      <c r="J62" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" t="s">
-        <v>359</v>
-      </c>
-      <c r="B63" t="s">
-        <v>360</v>
-      </c>
-      <c r="C63" t="s">
-        <v>33</v>
-      </c>
-      <c r="E63" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" t="s">
-        <v>152</v>
-      </c>
-      <c r="I63" t="s">
-        <v>361</v>
-      </c>
-      <c r="J63" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" t="s">
-        <v>363</v>
-      </c>
-      <c r="B64" t="s">
-        <v>364</v>
-      </c>
-      <c r="C64" t="s">
-        <v>33</v>
-      </c>
-      <c r="E64" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" t="s">
-        <v>152</v>
-      </c>
-      <c r="I64" t="s">
-        <v>365</v>
-      </c>
-      <c r="J64" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" t="s">
-        <v>367</v>
-      </c>
-      <c r="B65" t="s">
-        <v>368</v>
-      </c>
-      <c r="C65" t="s">
-        <v>33</v>
-      </c>
-      <c r="E65" t="s">
-        <v>52</v>
-      </c>
-      <c r="H65" t="s">
-        <v>152</v>
-      </c>
-      <c r="I65" t="s">
-        <v>369</v>
-      </c>
-      <c r="J65" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66" t="s">
-        <v>371</v>
-      </c>
-      <c r="B66" t="s">
-        <v>372</v>
-      </c>
-      <c r="C66" t="s">
-        <v>33</v>
-      </c>
-      <c r="E66" t="s">
-        <v>52</v>
-      </c>
-      <c r="H66" t="s">
-        <v>152</v>
-      </c>
-      <c r="I66" t="s">
-        <v>373</v>
-      </c>
-      <c r="J66" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>375</v>
-      </c>
-      <c r="B67" t="s">
-        <v>376</v>
-      </c>
-      <c r="C67" t="s">
-        <v>36</v>
-      </c>
-      <c r="E67" t="s">
-        <v>52</v>
-      </c>
-      <c r="H67" t="s">
-        <v>152</v>
-      </c>
-      <c r="I67" t="s">
-        <v>377</v>
-      </c>
-      <c r="J67" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>379</v>
-      </c>
-      <c r="B68" t="s">
-        <v>380</v>
-      </c>
-      <c r="C68" t="s">
-        <v>36</v>
-      </c>
-      <c r="E68" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" t="s">
-        <v>152</v>
-      </c>
-      <c r="I68" t="s">
-        <v>381</v>
-      </c>
-      <c r="J68" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" t="s">
-        <v>383</v>
-      </c>
-      <c r="B69" t="s">
-        <v>384</v>
-      </c>
-      <c r="C69" t="s">
-        <v>36</v>
-      </c>
-      <c r="E69" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" t="s">
-        <v>152</v>
-      </c>
-      <c r="I69" t="s">
-        <v>385</v>
-      </c>
-      <c r="J69" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" t="s">
-        <v>387</v>
-      </c>
-      <c r="B70" t="s">
-        <v>388</v>
-      </c>
-      <c r="C70" t="s">
-        <v>36</v>
-      </c>
-      <c r="E70" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" t="s">
-        <v>152</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="D76" s="11"/>
+      <c r="E76" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="J70" t="s">
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I76" s="12" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" t="s">
+      <c r="J76" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="B71" t="s">
+    </row>
+    <row r="77" ht="64" customHeight="1" spans="1:15">
+      <c r="A77" s="11">
+        <v>75</v>
+      </c>
+      <c r="B77" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="C71" t="s">
-        <v>36</v>
-      </c>
-      <c r="E71" t="s">
-        <v>52</v>
-      </c>
-      <c r="H71" t="s">
-        <v>152</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="C77" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="J71" t="s">
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I77" s="12" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" t="s">
+      <c r="J77" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="B72" t="s">
+    </row>
+    <row r="78" ht="64" customHeight="1" spans="1:15">
+      <c r="A78" s="11">
+        <v>76</v>
+      </c>
+      <c r="B78" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="C72" t="s">
-        <v>36</v>
-      </c>
-      <c r="E72" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" t="s">
-        <v>152</v>
-      </c>
-      <c r="I72" t="s">
+      <c r="C78" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="J72" t="s">
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I78" s="12" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" t="s">
+      <c r="J78" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="B73" t="s">
+    </row>
+    <row r="79" ht="83.25" spans="1:15">
+      <c r="A79" s="11">
+        <v>77</v>
+      </c>
+      <c r="B79" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="C73" t="s">
-        <v>36</v>
-      </c>
-      <c r="E73" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" t="s">
-        <v>152</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="C79" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="J73" t="s">
+      <c r="D79" s="12" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" t="s">
+      <c r="E79" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="B74" t="s">
+      <c r="F79" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="C74" t="s">
-        <v>36</v>
-      </c>
-      <c r="E74" t="s">
-        <v>13</v>
-      </c>
-      <c r="H74" t="s">
-        <v>152</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="J79" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K79" s="11"/>
+      <c r="L79" s="12"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="12"/>
+      <c r="O79" s="11"/>
+    </row>
+    <row r="80" ht="83.25" spans="1:15">
+      <c r="A80" s="11">
+        <v>78</v>
+      </c>
+      <c r="B80" s="12" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" t="s">
+      <c r="C80" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E80" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="B75" t="s">
+      <c r="F80" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="C75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E75" t="s">
-        <v>13</v>
-      </c>
-      <c r="H75" t="s">
-        <v>152</v>
-      </c>
-      <c r="I75" t="s">
+      <c r="J80" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K80" s="11"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="12"/>
+      <c r="O80" s="11"/>
+    </row>
+    <row r="81" ht="69.4" spans="1:15">
+      <c r="A81" s="11">
+        <v>79</v>
+      </c>
+      <c r="B81" s="12" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" t="s">
+      <c r="C81" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E81" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="B76" t="s">
+      <c r="F81" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="C76" t="s">
-        <v>36</v>
-      </c>
-      <c r="E76" t="s">
-        <v>52</v>
-      </c>
-      <c r="H76" t="s">
-        <v>152</v>
-      </c>
-      <c r="I76" t="s">
+      <c r="J81" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K81" s="11"/>
+      <c r="L81" s="12"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="11"/>
+    </row>
+    <row r="82" ht="69.4" spans="1:15">
+      <c r="A82" s="11">
+        <v>80</v>
+      </c>
+      <c r="B82" s="12" t="s">
         <v>414</v>
       </c>
+      <c r="C82" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="K82" s="11"/>
+      <c r="L82" s="12"/>
+      <c r="M82" s="11"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="11"/>
+    </row>
+    <row r="83" ht="97.15" spans="1:15">
+      <c r="A83" s="11">
+        <v>81</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H83" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="K83" s="11"/>
+      <c r="L83" s="12"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="12"/>
+      <c r="O83" s="11"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:J83" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -5165,6 +6582,1810 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:J76"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="39.6991150442478" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.716814159292" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.2920353982301" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.8230088495575" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.1504424778761" style="1" customWidth="1"/>
+    <col min="10" max="10" width="40.4955752212389" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="14.65" customHeight="1" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="54" customHeight="1" spans="1:10">
+      <c r="A3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46307</v>
+      </c>
+      <c r="G3" s="5">
+        <v>46307</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4" ht="40.5" customHeight="1" spans="1:10">
+      <c r="A4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="5">
+        <v>46307</v>
+      </c>
+      <c r="G4" s="5">
+        <v>46307</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>429</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="5" ht="40.5" customHeight="1" spans="1:10">
+      <c r="A5" t="s">
+        <v>431</v>
+      </c>
+      <c r="B5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46308</v>
+      </c>
+      <c r="G5" s="5">
+        <v>46309</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>433</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1" spans="1:10">
+      <c r="A6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5">
+        <v>46309</v>
+      </c>
+      <c r="G6" s="5">
+        <v>46309</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>437</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" ht="67.5" customHeight="1" spans="1:10">
+      <c r="A7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="5">
+        <v>46309</v>
+      </c>
+      <c r="G7" s="5">
+        <v>46307</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>440</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1" spans="1:10">
+      <c r="A8" t="s">
+        <v>442</v>
+      </c>
+      <c r="B8" t="s">
+        <v>443</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="5">
+        <v>46310</v>
+      </c>
+      <c r="G8" s="5">
+        <v>46311</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>444</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>446</v>
+      </c>
+      <c r="B9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="5">
+        <v>46311</v>
+      </c>
+      <c r="G9" s="5">
+        <v>46311</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1" spans="1:10">
+      <c r="A10" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="8">
+        <v>46311</v>
+      </c>
+      <c r="G10" s="8">
+        <v>46315</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>453</v>
+      </c>
+      <c r="B11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="5">
+        <v>46315</v>
+      </c>
+      <c r="G11" s="5">
+        <v>46316</v>
+      </c>
+      <c r="H11" t="s">
+        <v>276</v>
+      </c>
+      <c r="I11" t="s">
+        <v>455</v>
+      </c>
+      <c r="J11" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>457</v>
+      </c>
+      <c r="B12" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="5">
+        <v>46316</v>
+      </c>
+      <c r="G12" s="5">
+        <v>46317</v>
+      </c>
+      <c r="H12" t="s">
+        <v>276</v>
+      </c>
+      <c r="I12" t="s">
+        <v>459</v>
+      </c>
+      <c r="J12" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>276</v>
+      </c>
+      <c r="I13" t="s">
+        <v>462</v>
+      </c>
+      <c r="J13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>464</v>
+      </c>
+      <c r="B14" t="s">
+        <v>465</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>276</v>
+      </c>
+      <c r="I14" t="s">
+        <v>466</v>
+      </c>
+      <c r="J14" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>468</v>
+      </c>
+      <c r="B15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>276</v>
+      </c>
+      <c r="I15" t="s">
+        <v>470</v>
+      </c>
+      <c r="J15" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>472</v>
+      </c>
+      <c r="B16" t="s">
+        <v>473</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I16" t="s">
+        <v>474</v>
+      </c>
+      <c r="J16" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>476</v>
+      </c>
+      <c r="B17" t="s">
+        <v>477</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>276</v>
+      </c>
+      <c r="I17" t="s">
+        <v>478</v>
+      </c>
+      <c r="J17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>480</v>
+      </c>
+      <c r="B18" t="s">
+        <v>481</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>276</v>
+      </c>
+      <c r="I18" t="s">
+        <v>482</v>
+      </c>
+      <c r="J18" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>484</v>
+      </c>
+      <c r="B19" t="s">
+        <v>485</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>276</v>
+      </c>
+      <c r="I19" t="s">
+        <v>486</v>
+      </c>
+      <c r="J19" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>488</v>
+      </c>
+      <c r="B20" t="s">
+        <v>489</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" t="s">
+        <v>276</v>
+      </c>
+      <c r="I20" t="s">
+        <v>490</v>
+      </c>
+      <c r="J20" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>492</v>
+      </c>
+      <c r="B21" t="s">
+        <v>493</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>276</v>
+      </c>
+      <c r="I21" t="s">
+        <v>494</v>
+      </c>
+      <c r="J21" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>496</v>
+      </c>
+      <c r="B22" t="s">
+        <v>497</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
+        <v>276</v>
+      </c>
+      <c r="I22" t="s">
+        <v>498</v>
+      </c>
+      <c r="J22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>500</v>
+      </c>
+      <c r="B23" t="s">
+        <v>501</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" t="s">
+        <v>276</v>
+      </c>
+      <c r="I23" t="s">
+        <v>502</v>
+      </c>
+      <c r="J23" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>504</v>
+      </c>
+      <c r="B24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" t="s">
+        <v>276</v>
+      </c>
+      <c r="I24" t="s">
+        <v>505</v>
+      </c>
+      <c r="J24" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>507</v>
+      </c>
+      <c r="B25" t="s">
+        <v>508</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" t="s">
+        <v>276</v>
+      </c>
+      <c r="I25" t="s">
+        <v>509</v>
+      </c>
+      <c r="J25" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>511</v>
+      </c>
+      <c r="B26" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" t="s">
+        <v>276</v>
+      </c>
+      <c r="I26" t="s">
+        <v>512</v>
+      </c>
+      <c r="J26" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>514</v>
+      </c>
+      <c r="B27" t="s">
+        <v>515</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>276</v>
+      </c>
+      <c r="I27" t="s">
+        <v>516</v>
+      </c>
+      <c r="J27" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>518</v>
+      </c>
+      <c r="B28" t="s">
+        <v>519</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" t="s">
+        <v>276</v>
+      </c>
+      <c r="I28" t="s">
+        <v>520</v>
+      </c>
+      <c r="J28" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>522</v>
+      </c>
+      <c r="B29" t="s">
+        <v>523</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>276</v>
+      </c>
+      <c r="I29" t="s">
+        <v>524</v>
+      </c>
+      <c r="J29" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>526</v>
+      </c>
+      <c r="B30" t="s">
+        <v>527</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" t="s">
+        <v>276</v>
+      </c>
+      <c r="I30" t="s">
+        <v>528</v>
+      </c>
+      <c r="J30" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>530</v>
+      </c>
+      <c r="B31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>276</v>
+      </c>
+      <c r="I31" t="s">
+        <v>532</v>
+      </c>
+      <c r="J31" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>534</v>
+      </c>
+      <c r="B32" t="s">
+        <v>535</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" t="s">
+        <v>276</v>
+      </c>
+      <c r="I32" t="s">
+        <v>536</v>
+      </c>
+      <c r="J32" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>538</v>
+      </c>
+      <c r="B33" t="s">
+        <v>539</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" t="s">
+        <v>276</v>
+      </c>
+      <c r="I33" t="s">
+        <v>540</v>
+      </c>
+      <c r="J33" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>542</v>
+      </c>
+      <c r="B34" t="s">
+        <v>226</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>276</v>
+      </c>
+      <c r="I34" t="s">
+        <v>543</v>
+      </c>
+      <c r="J34" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>545</v>
+      </c>
+      <c r="B35" t="s">
+        <v>546</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" t="s">
+        <v>276</v>
+      </c>
+      <c r="I35" t="s">
+        <v>547</v>
+      </c>
+      <c r="J35" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>549</v>
+      </c>
+      <c r="B36" t="s">
+        <v>550</v>
+      </c>
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
+        <v>276</v>
+      </c>
+      <c r="I36" t="s">
+        <v>551</v>
+      </c>
+      <c r="J36" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>553</v>
+      </c>
+      <c r="B37" t="s">
+        <v>554</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>276</v>
+      </c>
+      <c r="I37" t="s">
+        <v>555</v>
+      </c>
+      <c r="J37" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>557</v>
+      </c>
+      <c r="B38" t="s">
+        <v>558</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" t="s">
+        <v>276</v>
+      </c>
+      <c r="I38" t="s">
+        <v>559</v>
+      </c>
+      <c r="J38" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>561</v>
+      </c>
+      <c r="B39" t="s">
+        <v>562</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>276</v>
+      </c>
+      <c r="I39" t="s">
+        <v>563</v>
+      </c>
+      <c r="J39" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>565</v>
+      </c>
+      <c r="B40" t="s">
+        <v>566</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>276</v>
+      </c>
+      <c r="I40" t="s">
+        <v>567</v>
+      </c>
+      <c r="J40" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>569</v>
+      </c>
+      <c r="B41" t="s">
+        <v>570</v>
+      </c>
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>276</v>
+      </c>
+      <c r="I41" t="s">
+        <v>571</v>
+      </c>
+      <c r="J41" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>573</v>
+      </c>
+      <c r="B42" t="s">
+        <v>574</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" t="s">
+        <v>276</v>
+      </c>
+      <c r="I42" t="s">
+        <v>575</v>
+      </c>
+      <c r="J42" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>577</v>
+      </c>
+      <c r="B43" t="s">
+        <v>578</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>276</v>
+      </c>
+      <c r="I43" t="s">
+        <v>579</v>
+      </c>
+      <c r="J43" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>581</v>
+      </c>
+      <c r="B44" t="s">
+        <v>582</v>
+      </c>
+      <c r="C44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>276</v>
+      </c>
+      <c r="I44" t="s">
+        <v>583</v>
+      </c>
+      <c r="J44" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>585</v>
+      </c>
+      <c r="B45" t="s">
+        <v>586</v>
+      </c>
+      <c r="C45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" t="s">
+        <v>276</v>
+      </c>
+      <c r="I45" t="s">
+        <v>587</v>
+      </c>
+      <c r="J45" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>589</v>
+      </c>
+      <c r="B46" t="s">
+        <v>590</v>
+      </c>
+      <c r="C46" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
+        <v>276</v>
+      </c>
+      <c r="I46" t="s">
+        <v>591</v>
+      </c>
+      <c r="J46" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>593</v>
+      </c>
+      <c r="B47" t="s">
+        <v>594</v>
+      </c>
+      <c r="C47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" t="s">
+        <v>276</v>
+      </c>
+      <c r="I47" t="s">
+        <v>595</v>
+      </c>
+      <c r="J47" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>597</v>
+      </c>
+      <c r="B48" t="s">
+        <v>598</v>
+      </c>
+      <c r="C48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>52</v>
+      </c>
+      <c r="H48" t="s">
+        <v>276</v>
+      </c>
+      <c r="I48" t="s">
+        <v>599</v>
+      </c>
+      <c r="J48" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>601</v>
+      </c>
+      <c r="B49" t="s">
+        <v>602</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>52</v>
+      </c>
+      <c r="H49" t="s">
+        <v>276</v>
+      </c>
+      <c r="I49" t="s">
+        <v>603</v>
+      </c>
+      <c r="J49" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>605</v>
+      </c>
+      <c r="B50" t="s">
+        <v>606</v>
+      </c>
+      <c r="C50" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>276</v>
+      </c>
+      <c r="I50" t="s">
+        <v>607</v>
+      </c>
+      <c r="J50" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>609</v>
+      </c>
+      <c r="B51" t="s">
+        <v>610</v>
+      </c>
+      <c r="C51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" t="s">
+        <v>52</v>
+      </c>
+      <c r="H51" t="s">
+        <v>276</v>
+      </c>
+      <c r="I51" t="s">
+        <v>611</v>
+      </c>
+      <c r="J51" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>613</v>
+      </c>
+      <c r="B52" t="s">
+        <v>293</v>
+      </c>
+      <c r="C52" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" t="s">
+        <v>52</v>
+      </c>
+      <c r="H52" t="s">
+        <v>276</v>
+      </c>
+      <c r="I52" t="s">
+        <v>614</v>
+      </c>
+      <c r="J52" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>616</v>
+      </c>
+      <c r="B53" t="s">
+        <v>617</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>276</v>
+      </c>
+      <c r="I53" t="s">
+        <v>618</v>
+      </c>
+      <c r="J53" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>620</v>
+      </c>
+      <c r="B54" t="s">
+        <v>621</v>
+      </c>
+      <c r="C54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>276</v>
+      </c>
+      <c r="I54" t="s">
+        <v>622</v>
+      </c>
+      <c r="J54" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>624</v>
+      </c>
+      <c r="B55" t="s">
+        <v>625</v>
+      </c>
+      <c r="C55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" t="s">
+        <v>276</v>
+      </c>
+      <c r="I55" t="s">
+        <v>626</v>
+      </c>
+      <c r="J55" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>628</v>
+      </c>
+      <c r="B56" t="s">
+        <v>629</v>
+      </c>
+      <c r="C56" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>276</v>
+      </c>
+      <c r="I56" t="s">
+        <v>630</v>
+      </c>
+      <c r="J56" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>632</v>
+      </c>
+      <c r="B57" t="s">
+        <v>633</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" t="s">
+        <v>52</v>
+      </c>
+      <c r="H57" t="s">
+        <v>276</v>
+      </c>
+      <c r="I57" t="s">
+        <v>634</v>
+      </c>
+      <c r="J57" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>636</v>
+      </c>
+      <c r="B58" t="s">
+        <v>637</v>
+      </c>
+      <c r="C58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
+        <v>276</v>
+      </c>
+      <c r="I58" t="s">
+        <v>638</v>
+      </c>
+      <c r="J58" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>640</v>
+      </c>
+      <c r="B59" t="s">
+        <v>641</v>
+      </c>
+      <c r="C59" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" t="s">
+        <v>276</v>
+      </c>
+      <c r="I59" t="s">
+        <v>642</v>
+      </c>
+      <c r="J59" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>644</v>
+      </c>
+      <c r="B60" t="s">
+        <v>645</v>
+      </c>
+      <c r="C60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>276</v>
+      </c>
+      <c r="I60" t="s">
+        <v>646</v>
+      </c>
+      <c r="J60" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>648</v>
+      </c>
+      <c r="B61" t="s">
+        <v>328</v>
+      </c>
+      <c r="C61" t="s">
+        <v>33</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" t="s">
+        <v>276</v>
+      </c>
+      <c r="I61" t="s">
+        <v>649</v>
+      </c>
+      <c r="J61" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>651</v>
+      </c>
+      <c r="B62" t="s">
+        <v>652</v>
+      </c>
+      <c r="C62" t="s">
+        <v>33</v>
+      </c>
+      <c r="E62" t="s">
+        <v>52</v>
+      </c>
+      <c r="H62" t="s">
+        <v>276</v>
+      </c>
+      <c r="I62" t="s">
+        <v>653</v>
+      </c>
+      <c r="J62" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>655</v>
+      </c>
+      <c r="B63" t="s">
+        <v>656</v>
+      </c>
+      <c r="C63" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
+        <v>276</v>
+      </c>
+      <c r="I63" t="s">
+        <v>657</v>
+      </c>
+      <c r="J63" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>659</v>
+      </c>
+      <c r="B64" t="s">
+        <v>660</v>
+      </c>
+      <c r="C64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" t="s">
+        <v>276</v>
+      </c>
+      <c r="I64" t="s">
+        <v>661</v>
+      </c>
+      <c r="J64" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>663</v>
+      </c>
+      <c r="B65" t="s">
+        <v>664</v>
+      </c>
+      <c r="C65" t="s">
+        <v>33</v>
+      </c>
+      <c r="E65" t="s">
+        <v>52</v>
+      </c>
+      <c r="H65" t="s">
+        <v>276</v>
+      </c>
+      <c r="I65" t="s">
+        <v>665</v>
+      </c>
+      <c r="J65" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>667</v>
+      </c>
+      <c r="B66" t="s">
+        <v>668</v>
+      </c>
+      <c r="C66" t="s">
+        <v>33</v>
+      </c>
+      <c r="E66" t="s">
+        <v>52</v>
+      </c>
+      <c r="H66" t="s">
+        <v>276</v>
+      </c>
+      <c r="I66" t="s">
+        <v>669</v>
+      </c>
+      <c r="J66" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>671</v>
+      </c>
+      <c r="B67" t="s">
+        <v>672</v>
+      </c>
+      <c r="C67" t="s">
+        <v>36</v>
+      </c>
+      <c r="E67" t="s">
+        <v>52</v>
+      </c>
+      <c r="H67" t="s">
+        <v>276</v>
+      </c>
+      <c r="I67" t="s">
+        <v>673</v>
+      </c>
+      <c r="J67" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>675</v>
+      </c>
+      <c r="B68" t="s">
+        <v>676</v>
+      </c>
+      <c r="C68" t="s">
+        <v>36</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
+        <v>276</v>
+      </c>
+      <c r="I68" t="s">
+        <v>677</v>
+      </c>
+      <c r="J68" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>679</v>
+      </c>
+      <c r="B69" t="s">
+        <v>680</v>
+      </c>
+      <c r="C69" t="s">
+        <v>36</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
+        <v>276</v>
+      </c>
+      <c r="I69" t="s">
+        <v>681</v>
+      </c>
+      <c r="J69" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>683</v>
+      </c>
+      <c r="B70" t="s">
+        <v>684</v>
+      </c>
+      <c r="C70" t="s">
+        <v>36</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
+        <v>276</v>
+      </c>
+      <c r="I70" t="s">
+        <v>685</v>
+      </c>
+      <c r="J70" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>687</v>
+      </c>
+      <c r="B71" t="s">
+        <v>366</v>
+      </c>
+      <c r="C71" t="s">
+        <v>36</v>
+      </c>
+      <c r="E71" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" t="s">
+        <v>276</v>
+      </c>
+      <c r="I71" t="s">
+        <v>688</v>
+      </c>
+      <c r="J71" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>690</v>
+      </c>
+      <c r="B72" t="s">
+        <v>691</v>
+      </c>
+      <c r="C72" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" t="s">
+        <v>276</v>
+      </c>
+      <c r="I72" t="s">
+        <v>692</v>
+      </c>
+      <c r="J72" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>694</v>
+      </c>
+      <c r="B73" t="s">
+        <v>695</v>
+      </c>
+      <c r="C73" t="s">
+        <v>36</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" t="s">
+        <v>276</v>
+      </c>
+      <c r="I73" t="s">
+        <v>696</v>
+      </c>
+      <c r="J73" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>698</v>
+      </c>
+      <c r="B74" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" t="s">
+        <v>36</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s">
+        <v>276</v>
+      </c>
+      <c r="I74" t="s">
+        <v>699</v>
+      </c>
+      <c r="J74" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>701</v>
+      </c>
+      <c r="B75" t="s">
+        <v>702</v>
+      </c>
+      <c r="C75" t="s">
+        <v>36</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" t="s">
+        <v>276</v>
+      </c>
+      <c r="I75" t="s">
+        <v>703</v>
+      </c>
+      <c r="J75" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>705</v>
+      </c>
+      <c r="B76" t="s">
+        <v>385</v>
+      </c>
+      <c r="C76" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76" t="s">
+        <v>52</v>
+      </c>
+      <c r="H76" t="s">
+        <v>276</v>
+      </c>
+      <c r="I76" t="s">
+        <v>706</v>
+      </c>
+      <c r="J76" t="s">
+        <v>707</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C3:C9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
